--- a/diseases/d063/2020-2025.xlsx
+++ b/diseases/d063/2020-2025.xlsx
@@ -996,7 +996,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
@@ -1607,7 +1607,7 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
@@ -2218,7 +2218,7 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
@@ -2829,7 +2829,7 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
@@ -3440,7 +3440,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
@@ -4051,7 +4051,7 @@
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
@@ -4662,7 +4662,7 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
@@ -5273,7 +5273,7 @@
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK24" t="inlineStr">
@@ -5884,7 +5884,7 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
@@ -6495,7 +6495,7 @@
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK30" t="inlineStr">
@@ -7106,7 +7106,7 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
@@ -7717,7 +7717,7 @@
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK36" t="inlineStr">
@@ -8328,7 +8328,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK39" t="inlineStr">
@@ -8716,7 +8716,7 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK41" t="inlineStr">
@@ -9104,7 +9104,7 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK43" t="inlineStr">
@@ -9492,7 +9492,7 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK45" t="inlineStr">
@@ -9880,7 +9880,7 @@
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK47" t="inlineStr">
@@ -10268,7 +10268,7 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK49" t="inlineStr">
@@ -10656,7 +10656,7 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK51" t="inlineStr">
@@ -11044,7 +11044,7 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK53" t="inlineStr">
@@ -11432,7 +11432,7 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK55" t="inlineStr">
@@ -11820,7 +11820,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK57" t="inlineStr">
@@ -12208,7 +12208,7 @@
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK59" t="inlineStr">
@@ -12596,7 +12596,7 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK61" t="inlineStr">
@@ -12984,7 +12984,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK63" t="inlineStr">
@@ -13372,7 +13372,7 @@
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK65" t="inlineStr">
@@ -13760,7 +13760,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK67" t="inlineStr">
@@ -14148,7 +14148,7 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK69" t="inlineStr">
@@ -14536,7 +14536,7 @@
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK71" t="inlineStr">
@@ -14924,7 +14924,7 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK73" t="inlineStr">
@@ -15312,7 +15312,7 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK75" t="inlineStr">
@@ -15700,7 +15700,7 @@
       </c>
       <c r="AJ77" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK77" t="inlineStr">
@@ -16088,7 +16088,7 @@
       </c>
       <c r="AJ79" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK79" t="inlineStr">
@@ -16476,7 +16476,7 @@
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK81" t="inlineStr">
@@ -16864,7 +16864,7 @@
       </c>
       <c r="AJ83" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK83" t="inlineStr">
@@ -17252,7 +17252,7 @@
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK85" t="inlineStr">
@@ -17640,7 +17640,7 @@
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK87" t="inlineStr">
@@ -18028,7 +18028,7 @@
       </c>
       <c r="AJ89" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK89" t="inlineStr">
@@ -18416,7 +18416,7 @@
       </c>
       <c r="AJ91" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK91" t="inlineStr">
@@ -18804,7 +18804,7 @@
       </c>
       <c r="AJ93" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK93" t="inlineStr">
@@ -19192,7 +19192,7 @@
       </c>
       <c r="AJ95" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK95" t="inlineStr">
@@ -19580,7 +19580,7 @@
       </c>
       <c r="AJ97" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK97" t="inlineStr">
@@ -19968,7 +19968,7 @@
       </c>
       <c r="AJ99" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK99" t="inlineStr">
@@ -20356,7 +20356,7 @@
       </c>
       <c r="AJ101" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK101" t="inlineStr">
@@ -20744,7 +20744,7 @@
       </c>
       <c r="AJ103" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK103" t="inlineStr">
@@ -21132,7 +21132,7 @@
       </c>
       <c r="AJ105" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK105" t="inlineStr">
@@ -21520,7 +21520,7 @@
       </c>
       <c r="AJ107" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK107" t="inlineStr">
@@ -21908,7 +21908,7 @@
       </c>
       <c r="AJ109" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK109" t="inlineStr">
@@ -22296,7 +22296,7 @@
       </c>
       <c r="AJ111" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK111" t="inlineStr">
@@ -22684,7 +22684,7 @@
       </c>
       <c r="AJ113" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK113" t="inlineStr">
@@ -23072,7 +23072,7 @@
       </c>
       <c r="AJ115" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK115" t="inlineStr">
@@ -23460,7 +23460,7 @@
       </c>
       <c r="AJ117" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK117" t="inlineStr">
@@ -23848,7 +23848,7 @@
       </c>
       <c r="AJ119" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK119" t="inlineStr">
@@ -24236,7 +24236,7 @@
       </c>
       <c r="AJ121" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK121" t="inlineStr">
@@ -24624,7 +24624,7 @@
       </c>
       <c r="AJ123" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK123" t="inlineStr">
@@ -25012,7 +25012,7 @@
       </c>
       <c r="AJ125" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK125" t="inlineStr">
@@ -25400,7 +25400,7 @@
       </c>
       <c r="AJ127" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK127" t="inlineStr">
@@ -25788,7 +25788,7 @@
       </c>
       <c r="AJ129" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK129" t="inlineStr">
@@ -26176,7 +26176,7 @@
       </c>
       <c r="AJ131" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK131" t="inlineStr">
@@ -26564,7 +26564,7 @@
       </c>
       <c r="AJ133" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK133" t="inlineStr">
@@ -26952,7 +26952,7 @@
       </c>
       <c r="AJ135" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK135" t="inlineStr">
@@ -27340,7 +27340,7 @@
       </c>
       <c r="AJ137" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK137" t="inlineStr">
@@ -27728,7 +27728,7 @@
       </c>
       <c r="AJ139" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK139" t="inlineStr">
@@ -28116,7 +28116,7 @@
       </c>
       <c r="AJ141" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK141" t="inlineStr">
@@ -28504,7 +28504,7 @@
       </c>
       <c r="AJ143" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK143" t="inlineStr">
@@ -28892,7 +28892,7 @@
       </c>
       <c r="AJ145" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK145" t="inlineStr">
@@ -29280,7 +29280,7 @@
       </c>
       <c r="AJ147" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK147" t="inlineStr">
@@ -29668,7 +29668,7 @@
       </c>
       <c r="AJ149" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK149" t="inlineStr">
@@ -30056,7 +30056,7 @@
       </c>
       <c r="AJ151" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK151" t="inlineStr">
@@ -30444,7 +30444,7 @@
       </c>
       <c r="AJ153" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK153" t="inlineStr">
@@ -30832,7 +30832,7 @@
       </c>
       <c r="AJ155" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK155" t="inlineStr">
@@ -31220,7 +31220,7 @@
       </c>
       <c r="AJ157" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK157" t="inlineStr">

--- a/diseases/d063/2020-2025.xlsx
+++ b/diseases/d063/2020-2025.xlsx
@@ -996,7 +996,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
@@ -1607,7 +1607,7 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
@@ -2218,7 +2218,7 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
@@ -2829,7 +2829,7 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
@@ -3440,7 +3440,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
@@ -4051,7 +4051,7 @@
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
@@ -4662,7 +4662,7 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
@@ -5273,7 +5273,7 @@
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK24" t="inlineStr">
@@ -5884,7 +5884,7 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
@@ -6495,7 +6495,7 @@
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK30" t="inlineStr">
@@ -7106,7 +7106,7 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
@@ -7717,7 +7717,7 @@
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK36" t="inlineStr">
@@ -8328,7 +8328,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK39" t="inlineStr">
@@ -8716,7 +8716,7 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK41" t="inlineStr">
@@ -9104,7 +9104,7 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK43" t="inlineStr">
@@ -9492,7 +9492,7 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK45" t="inlineStr">
@@ -9880,7 +9880,7 @@
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK47" t="inlineStr">
@@ -10268,7 +10268,7 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK49" t="inlineStr">
@@ -10656,7 +10656,7 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK51" t="inlineStr">
@@ -11044,7 +11044,7 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK53" t="inlineStr">
@@ -11432,7 +11432,7 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK55" t="inlineStr">
@@ -11820,7 +11820,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK57" t="inlineStr">
@@ -12208,7 +12208,7 @@
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK59" t="inlineStr">
@@ -12596,7 +12596,7 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK61" t="inlineStr">
@@ -12984,7 +12984,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK63" t="inlineStr">
@@ -13372,7 +13372,7 @@
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK65" t="inlineStr">
@@ -13760,7 +13760,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK67" t="inlineStr">
@@ -14148,7 +14148,7 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK69" t="inlineStr">
@@ -14536,7 +14536,7 @@
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK71" t="inlineStr">
@@ -14924,7 +14924,7 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK73" t="inlineStr">
@@ -15312,7 +15312,7 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK75" t="inlineStr">
@@ -15700,7 +15700,7 @@
       </c>
       <c r="AJ77" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK77" t="inlineStr">
@@ -16088,7 +16088,7 @@
       </c>
       <c r="AJ79" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK79" t="inlineStr">
@@ -16476,7 +16476,7 @@
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK81" t="inlineStr">
@@ -16864,7 +16864,7 @@
       </c>
       <c r="AJ83" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK83" t="inlineStr">
@@ -17252,7 +17252,7 @@
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK85" t="inlineStr">
@@ -17640,7 +17640,7 @@
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK87" t="inlineStr">
@@ -18028,7 +18028,7 @@
       </c>
       <c r="AJ89" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK89" t="inlineStr">
@@ -18416,7 +18416,7 @@
       </c>
       <c r="AJ91" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK91" t="inlineStr">
@@ -18804,7 +18804,7 @@
       </c>
       <c r="AJ93" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK93" t="inlineStr">
@@ -19192,7 +19192,7 @@
       </c>
       <c r="AJ95" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK95" t="inlineStr">
@@ -19580,7 +19580,7 @@
       </c>
       <c r="AJ97" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK97" t="inlineStr">
@@ -19968,7 +19968,7 @@
       </c>
       <c r="AJ99" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK99" t="inlineStr">
@@ -20356,7 +20356,7 @@
       </c>
       <c r="AJ101" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK101" t="inlineStr">
@@ -20744,7 +20744,7 @@
       </c>
       <c r="AJ103" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK103" t="inlineStr">
@@ -21132,7 +21132,7 @@
       </c>
       <c r="AJ105" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK105" t="inlineStr">
@@ -21520,7 +21520,7 @@
       </c>
       <c r="AJ107" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK107" t="inlineStr">
@@ -21908,7 +21908,7 @@
       </c>
       <c r="AJ109" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK109" t="inlineStr">
@@ -22296,7 +22296,7 @@
       </c>
       <c r="AJ111" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK111" t="inlineStr">
@@ -22684,7 +22684,7 @@
       </c>
       <c r="AJ113" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK113" t="inlineStr">
@@ -23072,7 +23072,7 @@
       </c>
       <c r="AJ115" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK115" t="inlineStr">
@@ -23460,7 +23460,7 @@
       </c>
       <c r="AJ117" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK117" t="inlineStr">
@@ -23848,7 +23848,7 @@
       </c>
       <c r="AJ119" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK119" t="inlineStr">
@@ -24236,7 +24236,7 @@
       </c>
       <c r="AJ121" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK121" t="inlineStr">
@@ -24624,7 +24624,7 @@
       </c>
       <c r="AJ123" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK123" t="inlineStr">
@@ -25012,7 +25012,7 @@
       </c>
       <c r="AJ125" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK125" t="inlineStr">
@@ -25400,7 +25400,7 @@
       </c>
       <c r="AJ127" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK127" t="inlineStr">
@@ -25788,7 +25788,7 @@
       </c>
       <c r="AJ129" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK129" t="inlineStr">
@@ -26176,7 +26176,7 @@
       </c>
       <c r="AJ131" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK131" t="inlineStr">
@@ -26564,7 +26564,7 @@
       </c>
       <c r="AJ133" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK133" t="inlineStr">
@@ -26952,7 +26952,7 @@
       </c>
       <c r="AJ135" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK135" t="inlineStr">
@@ -27340,7 +27340,7 @@
       </c>
       <c r="AJ137" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK137" t="inlineStr">
@@ -27728,7 +27728,7 @@
       </c>
       <c r="AJ139" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK139" t="inlineStr">
@@ -28116,7 +28116,7 @@
       </c>
       <c r="AJ141" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK141" t="inlineStr">
@@ -28504,7 +28504,7 @@
       </c>
       <c r="AJ143" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK143" t="inlineStr">
@@ -28892,7 +28892,7 @@
       </c>
       <c r="AJ145" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK145" t="inlineStr">
@@ -29280,7 +29280,7 @@
       </c>
       <c r="AJ147" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK147" t="inlineStr">
@@ -29668,7 +29668,7 @@
       </c>
       <c r="AJ149" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK149" t="inlineStr">
@@ -30056,7 +30056,7 @@
       </c>
       <c r="AJ151" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK151" t="inlineStr">
@@ -30444,7 +30444,7 @@
       </c>
       <c r="AJ153" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK153" t="inlineStr">
@@ -30832,7 +30832,7 @@
       </c>
       <c r="AJ155" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK155" t="inlineStr">
@@ -31220,7 +31220,7 @@
       </c>
       <c r="AJ157" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK157" t="inlineStr">

--- a/diseases/d063/2020-2025.xlsx
+++ b/diseases/d063/2020-2025.xlsx
@@ -1006,7 +1006,7 @@
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN3" t="b">
@@ -1617,7 +1617,7 @@
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN6" t="b">
@@ -2228,7 +2228,7 @@
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN9" t="b">
@@ -2839,7 +2839,7 @@
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN12" t="b">
@@ -3450,7 +3450,7 @@
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN15" t="b">
@@ -4061,7 +4061,7 @@
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN18" t="b">
@@ -4672,7 +4672,7 @@
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN21" t="b">
@@ -5283,7 +5283,7 @@
       </c>
       <c r="AM24" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN24" t="b">
@@ -5894,7 +5894,7 @@
       </c>
       <c r="AM27" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN27" t="b">
@@ -6505,7 +6505,7 @@
       </c>
       <c r="AM30" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN30" t="b">
@@ -7116,7 +7116,7 @@
       </c>
       <c r="AM33" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN33" t="b">
@@ -7727,7 +7727,7 @@
       </c>
       <c r="AM36" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN36" t="b">
@@ -8338,7 +8338,7 @@
       </c>
       <c r="AM39" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN39" t="b">
@@ -8726,7 +8726,7 @@
       </c>
       <c r="AM41" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN41" t="b">
@@ -9114,7 +9114,7 @@
       </c>
       <c r="AM43" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN43" t="b">
@@ -9502,7 +9502,7 @@
       </c>
       <c r="AM45" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN45" t="b">
@@ -9890,7 +9890,7 @@
       </c>
       <c r="AM47" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN47" t="b">
@@ -10278,7 +10278,7 @@
       </c>
       <c r="AM49" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN49" t="b">
@@ -10666,7 +10666,7 @@
       </c>
       <c r="AM51" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN51" t="b">
@@ -11054,7 +11054,7 @@
       </c>
       <c r="AM53" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN53" t="b">
@@ -11442,7 +11442,7 @@
       </c>
       <c r="AM55" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN55" t="b">
@@ -11830,7 +11830,7 @@
       </c>
       <c r="AM57" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN57" t="b">
@@ -12218,7 +12218,7 @@
       </c>
       <c r="AM59" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN59" t="b">
@@ -12606,7 +12606,7 @@
       </c>
       <c r="AM61" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN61" t="b">
@@ -12994,7 +12994,7 @@
       </c>
       <c r="AM63" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN63" t="b">
@@ -13382,7 +13382,7 @@
       </c>
       <c r="AM65" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN65" t="b">
@@ -13770,7 +13770,7 @@
       </c>
       <c r="AM67" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN67" t="b">
@@ -14158,7 +14158,7 @@
       </c>
       <c r="AM69" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN69" t="b">
@@ -14546,7 +14546,7 @@
       </c>
       <c r="AM71" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN71" t="b">
@@ -14934,7 +14934,7 @@
       </c>
       <c r="AM73" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN73" t="b">
@@ -15322,7 +15322,7 @@
       </c>
       <c r="AM75" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN75" t="b">
@@ -15710,7 +15710,7 @@
       </c>
       <c r="AM77" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN77" t="b">
@@ -16098,7 +16098,7 @@
       </c>
       <c r="AM79" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN79" t="b">
@@ -16486,7 +16486,7 @@
       </c>
       <c r="AM81" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN81" t="b">
@@ -16874,7 +16874,7 @@
       </c>
       <c r="AM83" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN83" t="b">
@@ -17262,7 +17262,7 @@
       </c>
       <c r="AM85" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN85" t="b">
@@ -17650,7 +17650,7 @@
       </c>
       <c r="AM87" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN87" t="b">
@@ -18038,7 +18038,7 @@
       </c>
       <c r="AM89" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN89" t="b">
@@ -18426,7 +18426,7 @@
       </c>
       <c r="AM91" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN91" t="b">
@@ -18814,7 +18814,7 @@
       </c>
       <c r="AM93" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN93" t="b">
@@ -19202,7 +19202,7 @@
       </c>
       <c r="AM95" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN95" t="b">
@@ -19590,7 +19590,7 @@
       </c>
       <c r="AM97" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN97" t="b">
@@ -19978,7 +19978,7 @@
       </c>
       <c r="AM99" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN99" t="b">
@@ -20366,7 +20366,7 @@
       </c>
       <c r="AM101" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN101" t="b">
@@ -20754,7 +20754,7 @@
       </c>
       <c r="AM103" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN103" t="b">
@@ -21142,7 +21142,7 @@
       </c>
       <c r="AM105" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN105" t="b">
@@ -21530,7 +21530,7 @@
       </c>
       <c r="AM107" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN107" t="b">
@@ -21918,7 +21918,7 @@
       </c>
       <c r="AM109" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN109" t="b">
@@ -22306,7 +22306,7 @@
       </c>
       <c r="AM111" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN111" t="b">
@@ -22694,7 +22694,7 @@
       </c>
       <c r="AM113" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN113" t="b">
@@ -23082,7 +23082,7 @@
       </c>
       <c r="AM115" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN115" t="b">
@@ -23470,7 +23470,7 @@
       </c>
       <c r="AM117" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN117" t="b">
@@ -23858,7 +23858,7 @@
       </c>
       <c r="AM119" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN119" t="b">
@@ -24246,7 +24246,7 @@
       </c>
       <c r="AM121" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN121" t="b">
@@ -24634,7 +24634,7 @@
       </c>
       <c r="AM123" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN123" t="b">
@@ -25022,7 +25022,7 @@
       </c>
       <c r="AM125" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN125" t="b">
@@ -25410,7 +25410,7 @@
       </c>
       <c r="AM127" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN127" t="b">
@@ -25798,7 +25798,7 @@
       </c>
       <c r="AM129" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN129" t="b">
@@ -26186,7 +26186,7 @@
       </c>
       <c r="AM131" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN131" t="b">
@@ -26574,7 +26574,7 @@
       </c>
       <c r="AM133" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN133" t="b">
@@ -26962,7 +26962,7 @@
       </c>
       <c r="AM135" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN135" t="b">
@@ -27350,7 +27350,7 @@
       </c>
       <c r="AM137" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN137" t="b">
@@ -27738,7 +27738,7 @@
       </c>
       <c r="AM139" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN139" t="b">
@@ -28126,7 +28126,7 @@
       </c>
       <c r="AM141" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN141" t="b">
@@ -28514,7 +28514,7 @@
       </c>
       <c r="AM143" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN143" t="b">
@@ -28902,7 +28902,7 @@
       </c>
       <c r="AM145" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN145" t="b">
@@ -29290,7 +29290,7 @@
       </c>
       <c r="AM147" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN147" t="b">
@@ -29678,7 +29678,7 @@
       </c>
       <c r="AM149" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN149" t="b">
@@ -30066,7 +30066,7 @@
       </c>
       <c r="AM151" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN151" t="b">
@@ -30454,7 +30454,7 @@
       </c>
       <c r="AM153" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN153" t="b">
@@ -30842,7 +30842,7 @@
       </c>
       <c r="AM155" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN155" t="b">
@@ -31230,7 +31230,7 @@
       </c>
       <c r="AM157" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN157" t="b">

--- a/diseases/d063/2020-2025.xlsx
+++ b/diseases/d063/2020-2025.xlsx
@@ -996,7 +996,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
@@ -1607,7 +1607,7 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
@@ -2218,7 +2218,7 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
@@ -2829,7 +2829,7 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
@@ -3440,7 +3440,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
@@ -4051,7 +4051,7 @@
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
@@ -4662,7 +4662,7 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
@@ -5273,7 +5273,7 @@
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK24" t="inlineStr">
@@ -5884,7 +5884,7 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
@@ -6495,7 +6495,7 @@
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK30" t="inlineStr">
@@ -7106,7 +7106,7 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
@@ -7717,7 +7717,7 @@
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK36" t="inlineStr">
@@ -8328,7 +8328,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK39" t="inlineStr">
@@ -8716,7 +8716,7 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK41" t="inlineStr">
@@ -9104,7 +9104,7 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK43" t="inlineStr">
@@ -9492,7 +9492,7 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK45" t="inlineStr">
@@ -9880,7 +9880,7 @@
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK47" t="inlineStr">
@@ -10268,7 +10268,7 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK49" t="inlineStr">
@@ -10656,7 +10656,7 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK51" t="inlineStr">
@@ -11044,7 +11044,7 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK53" t="inlineStr">
@@ -11432,7 +11432,7 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK55" t="inlineStr">
@@ -11820,7 +11820,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK57" t="inlineStr">
@@ -12208,7 +12208,7 @@
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK59" t="inlineStr">
@@ -12596,7 +12596,7 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK61" t="inlineStr">
@@ -12984,7 +12984,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK63" t="inlineStr">
@@ -13372,7 +13372,7 @@
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK65" t="inlineStr">
@@ -13760,7 +13760,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK67" t="inlineStr">
@@ -14148,7 +14148,7 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK69" t="inlineStr">
@@ -14536,7 +14536,7 @@
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK71" t="inlineStr">
@@ -14924,7 +14924,7 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK73" t="inlineStr">
@@ -15312,7 +15312,7 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK75" t="inlineStr">
@@ -15700,7 +15700,7 @@
       </c>
       <c r="AJ77" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK77" t="inlineStr">
@@ -16088,7 +16088,7 @@
       </c>
       <c r="AJ79" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK79" t="inlineStr">
@@ -16476,7 +16476,7 @@
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK81" t="inlineStr">
@@ -16864,7 +16864,7 @@
       </c>
       <c r="AJ83" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK83" t="inlineStr">
@@ -17252,7 +17252,7 @@
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK85" t="inlineStr">
@@ -17640,7 +17640,7 @@
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK87" t="inlineStr">
@@ -18028,7 +18028,7 @@
       </c>
       <c r="AJ89" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK89" t="inlineStr">
@@ -18416,7 +18416,7 @@
       </c>
       <c r="AJ91" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK91" t="inlineStr">
@@ -18804,7 +18804,7 @@
       </c>
       <c r="AJ93" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK93" t="inlineStr">
@@ -19192,7 +19192,7 @@
       </c>
       <c r="AJ95" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK95" t="inlineStr">
@@ -19580,7 +19580,7 @@
       </c>
       <c r="AJ97" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK97" t="inlineStr">
@@ -19968,7 +19968,7 @@
       </c>
       <c r="AJ99" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK99" t="inlineStr">
@@ -20356,7 +20356,7 @@
       </c>
       <c r="AJ101" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK101" t="inlineStr">
@@ -20744,7 +20744,7 @@
       </c>
       <c r="AJ103" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK103" t="inlineStr">
@@ -21132,7 +21132,7 @@
       </c>
       <c r="AJ105" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK105" t="inlineStr">
@@ -21520,7 +21520,7 @@
       </c>
       <c r="AJ107" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK107" t="inlineStr">
@@ -21908,7 +21908,7 @@
       </c>
       <c r="AJ109" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK109" t="inlineStr">
@@ -22296,7 +22296,7 @@
       </c>
       <c r="AJ111" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK111" t="inlineStr">
@@ -22684,7 +22684,7 @@
       </c>
       <c r="AJ113" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK113" t="inlineStr">
@@ -23072,7 +23072,7 @@
       </c>
       <c r="AJ115" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK115" t="inlineStr">
@@ -23460,7 +23460,7 @@
       </c>
       <c r="AJ117" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK117" t="inlineStr">
@@ -23848,7 +23848,7 @@
       </c>
       <c r="AJ119" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK119" t="inlineStr">
@@ -24236,7 +24236,7 @@
       </c>
       <c r="AJ121" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK121" t="inlineStr">
@@ -24624,7 +24624,7 @@
       </c>
       <c r="AJ123" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK123" t="inlineStr">
@@ -25012,7 +25012,7 @@
       </c>
       <c r="AJ125" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK125" t="inlineStr">
@@ -25400,7 +25400,7 @@
       </c>
       <c r="AJ127" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK127" t="inlineStr">
@@ -25788,7 +25788,7 @@
       </c>
       <c r="AJ129" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK129" t="inlineStr">
@@ -26176,7 +26176,7 @@
       </c>
       <c r="AJ131" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK131" t="inlineStr">
@@ -26564,7 +26564,7 @@
       </c>
       <c r="AJ133" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK133" t="inlineStr">
@@ -26952,7 +26952,7 @@
       </c>
       <c r="AJ135" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK135" t="inlineStr">
@@ -27340,7 +27340,7 @@
       </c>
       <c r="AJ137" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK137" t="inlineStr">
@@ -27728,7 +27728,7 @@
       </c>
       <c r="AJ139" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK139" t="inlineStr">
@@ -28116,7 +28116,7 @@
       </c>
       <c r="AJ141" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK141" t="inlineStr">
@@ -28504,7 +28504,7 @@
       </c>
       <c r="AJ143" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK143" t="inlineStr">
@@ -28892,7 +28892,7 @@
       </c>
       <c r="AJ145" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK145" t="inlineStr">
@@ -29280,7 +29280,7 @@
       </c>
       <c r="AJ147" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK147" t="inlineStr">
@@ -29668,7 +29668,7 @@
       </c>
       <c r="AJ149" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK149" t="inlineStr">
@@ -30056,7 +30056,7 @@
       </c>
       <c r="AJ151" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK151" t="inlineStr">
@@ -30444,7 +30444,7 @@
       </c>
       <c r="AJ153" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK153" t="inlineStr">
@@ -30832,7 +30832,7 @@
       </c>
       <c r="AJ155" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK155" t="inlineStr">
@@ -31220,7 +31220,7 @@
       </c>
       <c r="AJ157" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK157" t="inlineStr">

--- a/diseases/d063/2020-2025.xlsx
+++ b/diseases/d063/2020-2025.xlsx
@@ -996,7 +996,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
@@ -1607,7 +1607,7 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
@@ -2218,7 +2218,7 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
@@ -2829,7 +2829,7 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
@@ -3440,7 +3440,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
@@ -4051,7 +4051,7 @@
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
@@ -4662,7 +4662,7 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
@@ -5273,7 +5273,7 @@
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK24" t="inlineStr">
@@ -5884,7 +5884,7 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
@@ -6495,7 +6495,7 @@
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK30" t="inlineStr">
@@ -7106,7 +7106,7 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
@@ -7717,7 +7717,7 @@
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK36" t="inlineStr">
@@ -8328,7 +8328,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK39" t="inlineStr">
@@ -8716,7 +8716,7 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK41" t="inlineStr">
@@ -9104,7 +9104,7 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK43" t="inlineStr">
@@ -9492,7 +9492,7 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK45" t="inlineStr">
@@ -9880,7 +9880,7 @@
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK47" t="inlineStr">
@@ -10268,7 +10268,7 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK49" t="inlineStr">
@@ -10656,7 +10656,7 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK51" t="inlineStr">
@@ -11044,7 +11044,7 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK53" t="inlineStr">
@@ -11432,7 +11432,7 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK55" t="inlineStr">
@@ -11820,7 +11820,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK57" t="inlineStr">
@@ -12208,7 +12208,7 @@
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK59" t="inlineStr">
@@ -12596,7 +12596,7 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK61" t="inlineStr">
@@ -12984,7 +12984,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK63" t="inlineStr">
@@ -13372,7 +13372,7 @@
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK65" t="inlineStr">
@@ -13760,7 +13760,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK67" t="inlineStr">
@@ -14148,7 +14148,7 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK69" t="inlineStr">
@@ -14536,7 +14536,7 @@
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK71" t="inlineStr">
@@ -14924,7 +14924,7 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK73" t="inlineStr">
@@ -15312,7 +15312,7 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK75" t="inlineStr">
@@ -15700,7 +15700,7 @@
       </c>
       <c r="AJ77" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK77" t="inlineStr">
@@ -16088,7 +16088,7 @@
       </c>
       <c r="AJ79" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK79" t="inlineStr">
@@ -16476,7 +16476,7 @@
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK81" t="inlineStr">
@@ -16864,7 +16864,7 @@
       </c>
       <c r="AJ83" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK83" t="inlineStr">
@@ -17252,7 +17252,7 @@
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK85" t="inlineStr">
@@ -17640,7 +17640,7 @@
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK87" t="inlineStr">
@@ -18028,7 +18028,7 @@
       </c>
       <c r="AJ89" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK89" t="inlineStr">
@@ -18416,7 +18416,7 @@
       </c>
       <c r="AJ91" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK91" t="inlineStr">
@@ -18804,7 +18804,7 @@
       </c>
       <c r="AJ93" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK93" t="inlineStr">
@@ -19192,7 +19192,7 @@
       </c>
       <c r="AJ95" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK95" t="inlineStr">
@@ -19580,7 +19580,7 @@
       </c>
       <c r="AJ97" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK97" t="inlineStr">
@@ -19968,7 +19968,7 @@
       </c>
       <c r="AJ99" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK99" t="inlineStr">
@@ -20356,7 +20356,7 @@
       </c>
       <c r="AJ101" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK101" t="inlineStr">
@@ -20744,7 +20744,7 @@
       </c>
       <c r="AJ103" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK103" t="inlineStr">
@@ -21132,7 +21132,7 @@
       </c>
       <c r="AJ105" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK105" t="inlineStr">
@@ -21520,7 +21520,7 @@
       </c>
       <c r="AJ107" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK107" t="inlineStr">
@@ -21908,7 +21908,7 @@
       </c>
       <c r="AJ109" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK109" t="inlineStr">
@@ -22296,7 +22296,7 @@
       </c>
       <c r="AJ111" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK111" t="inlineStr">
@@ -22684,7 +22684,7 @@
       </c>
       <c r="AJ113" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK113" t="inlineStr">
@@ -23072,7 +23072,7 @@
       </c>
       <c r="AJ115" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK115" t="inlineStr">
@@ -23460,7 +23460,7 @@
       </c>
       <c r="AJ117" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK117" t="inlineStr">
@@ -23848,7 +23848,7 @@
       </c>
       <c r="AJ119" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK119" t="inlineStr">
@@ -24236,7 +24236,7 @@
       </c>
       <c r="AJ121" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK121" t="inlineStr">
@@ -24624,7 +24624,7 @@
       </c>
       <c r="AJ123" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK123" t="inlineStr">
@@ -25012,7 +25012,7 @@
       </c>
       <c r="AJ125" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK125" t="inlineStr">
@@ -25400,7 +25400,7 @@
       </c>
       <c r="AJ127" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK127" t="inlineStr">
@@ -25788,7 +25788,7 @@
       </c>
       <c r="AJ129" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK129" t="inlineStr">
@@ -26176,7 +26176,7 @@
       </c>
       <c r="AJ131" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK131" t="inlineStr">
@@ -26564,7 +26564,7 @@
       </c>
       <c r="AJ133" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK133" t="inlineStr">
@@ -26952,7 +26952,7 @@
       </c>
       <c r="AJ135" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK135" t="inlineStr">
@@ -27340,7 +27340,7 @@
       </c>
       <c r="AJ137" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK137" t="inlineStr">
@@ -27728,7 +27728,7 @@
       </c>
       <c r="AJ139" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK139" t="inlineStr">
@@ -28116,7 +28116,7 @@
       </c>
       <c r="AJ141" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK141" t="inlineStr">
@@ -28504,7 +28504,7 @@
       </c>
       <c r="AJ143" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK143" t="inlineStr">
@@ -28892,7 +28892,7 @@
       </c>
       <c r="AJ145" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK145" t="inlineStr">
@@ -29280,7 +29280,7 @@
       </c>
       <c r="AJ147" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK147" t="inlineStr">
@@ -29668,7 +29668,7 @@
       </c>
       <c r="AJ149" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK149" t="inlineStr">
@@ -30056,7 +30056,7 @@
       </c>
       <c r="AJ151" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK151" t="inlineStr">
@@ -30444,7 +30444,7 @@
       </c>
       <c r="AJ153" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK153" t="inlineStr">
@@ -30832,7 +30832,7 @@
       </c>
       <c r="AJ155" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK155" t="inlineStr">
@@ -31220,7 +31220,7 @@
       </c>
       <c r="AJ157" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK157" t="inlineStr">

--- a/diseases/d063/2020-2025.xlsx
+++ b/diseases/d063/2020-2025.xlsx
@@ -996,7 +996,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
@@ -1607,7 +1607,7 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
@@ -2218,7 +2218,7 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
@@ -2829,7 +2829,7 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
@@ -3440,7 +3440,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
@@ -4051,7 +4051,7 @@
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
@@ -4662,7 +4662,7 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
@@ -5273,7 +5273,7 @@
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK24" t="inlineStr">
@@ -5884,7 +5884,7 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
@@ -6495,7 +6495,7 @@
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK30" t="inlineStr">
@@ -7106,7 +7106,7 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
@@ -7717,7 +7717,7 @@
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK36" t="inlineStr">
@@ -8328,7 +8328,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK39" t="inlineStr">
@@ -8716,7 +8716,7 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK41" t="inlineStr">
@@ -9104,7 +9104,7 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK43" t="inlineStr">
@@ -9492,7 +9492,7 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK45" t="inlineStr">
@@ -9880,7 +9880,7 @@
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK47" t="inlineStr">
@@ -10268,7 +10268,7 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK49" t="inlineStr">
@@ -10656,7 +10656,7 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK51" t="inlineStr">
@@ -11044,7 +11044,7 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK53" t="inlineStr">
@@ -11432,7 +11432,7 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK55" t="inlineStr">
@@ -11820,7 +11820,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK57" t="inlineStr">
@@ -12208,7 +12208,7 @@
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK59" t="inlineStr">
@@ -12596,7 +12596,7 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK61" t="inlineStr">
@@ -12984,7 +12984,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK63" t="inlineStr">
@@ -13372,7 +13372,7 @@
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK65" t="inlineStr">
@@ -13760,7 +13760,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK67" t="inlineStr">
@@ -14148,7 +14148,7 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK69" t="inlineStr">
@@ -14536,7 +14536,7 @@
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK71" t="inlineStr">
@@ -14924,7 +14924,7 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK73" t="inlineStr">
@@ -15312,7 +15312,7 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK75" t="inlineStr">
@@ -15700,7 +15700,7 @@
       </c>
       <c r="AJ77" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK77" t="inlineStr">
@@ -16088,7 +16088,7 @@
       </c>
       <c r="AJ79" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK79" t="inlineStr">
@@ -16476,7 +16476,7 @@
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK81" t="inlineStr">
@@ -16864,7 +16864,7 @@
       </c>
       <c r="AJ83" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK83" t="inlineStr">
@@ -17252,7 +17252,7 @@
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK85" t="inlineStr">
@@ -17640,7 +17640,7 @@
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK87" t="inlineStr">
@@ -18028,7 +18028,7 @@
       </c>
       <c r="AJ89" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK89" t="inlineStr">
@@ -18416,7 +18416,7 @@
       </c>
       <c r="AJ91" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK91" t="inlineStr">
@@ -18804,7 +18804,7 @@
       </c>
       <c r="AJ93" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK93" t="inlineStr">
@@ -19192,7 +19192,7 @@
       </c>
       <c r="AJ95" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK95" t="inlineStr">
@@ -19580,7 +19580,7 @@
       </c>
       <c r="AJ97" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK97" t="inlineStr">
@@ -19968,7 +19968,7 @@
       </c>
       <c r="AJ99" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK99" t="inlineStr">
@@ -20356,7 +20356,7 @@
       </c>
       <c r="AJ101" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK101" t="inlineStr">
@@ -20744,7 +20744,7 @@
       </c>
       <c r="AJ103" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK103" t="inlineStr">
@@ -21132,7 +21132,7 @@
       </c>
       <c r="AJ105" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK105" t="inlineStr">
@@ -21520,7 +21520,7 @@
       </c>
       <c r="AJ107" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK107" t="inlineStr">
@@ -21908,7 +21908,7 @@
       </c>
       <c r="AJ109" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK109" t="inlineStr">
@@ -22296,7 +22296,7 @@
       </c>
       <c r="AJ111" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK111" t="inlineStr">
@@ -22684,7 +22684,7 @@
       </c>
       <c r="AJ113" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK113" t="inlineStr">
@@ -23072,7 +23072,7 @@
       </c>
       <c r="AJ115" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK115" t="inlineStr">
@@ -23460,7 +23460,7 @@
       </c>
       <c r="AJ117" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK117" t="inlineStr">
@@ -23848,7 +23848,7 @@
       </c>
       <c r="AJ119" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK119" t="inlineStr">
@@ -24236,7 +24236,7 @@
       </c>
       <c r="AJ121" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK121" t="inlineStr">
@@ -24624,7 +24624,7 @@
       </c>
       <c r="AJ123" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK123" t="inlineStr">
@@ -25012,7 +25012,7 @@
       </c>
       <c r="AJ125" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK125" t="inlineStr">
@@ -25400,7 +25400,7 @@
       </c>
       <c r="AJ127" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK127" t="inlineStr">
@@ -25788,7 +25788,7 @@
       </c>
       <c r="AJ129" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK129" t="inlineStr">
@@ -26176,7 +26176,7 @@
       </c>
       <c r="AJ131" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK131" t="inlineStr">
@@ -26564,7 +26564,7 @@
       </c>
       <c r="AJ133" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK133" t="inlineStr">
@@ -26952,7 +26952,7 @@
       </c>
       <c r="AJ135" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK135" t="inlineStr">
@@ -27340,7 +27340,7 @@
       </c>
       <c r="AJ137" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK137" t="inlineStr">
@@ -27728,7 +27728,7 @@
       </c>
       <c r="AJ139" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK139" t="inlineStr">
@@ -28116,7 +28116,7 @@
       </c>
       <c r="AJ141" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK141" t="inlineStr">
@@ -28504,7 +28504,7 @@
       </c>
       <c r="AJ143" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK143" t="inlineStr">
@@ -28892,7 +28892,7 @@
       </c>
       <c r="AJ145" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK145" t="inlineStr">
@@ -29280,7 +29280,7 @@
       </c>
       <c r="AJ147" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK147" t="inlineStr">
@@ -29668,7 +29668,7 @@
       </c>
       <c r="AJ149" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK149" t="inlineStr">
@@ -30056,7 +30056,7 @@
       </c>
       <c r="AJ151" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK151" t="inlineStr">
@@ -30444,7 +30444,7 @@
       </c>
       <c r="AJ153" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK153" t="inlineStr">
@@ -30832,7 +30832,7 @@
       </c>
       <c r="AJ155" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK155" t="inlineStr">
@@ -31220,7 +31220,7 @@
       </c>
       <c r="AJ157" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK157" t="inlineStr">

--- a/diseases/d063/2020-2025.xlsx
+++ b/diseases/d063/2020-2025.xlsx
@@ -996,7 +996,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
@@ -1607,7 +1607,7 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
@@ -2218,7 +2218,7 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
@@ -2829,7 +2829,7 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
@@ -3440,7 +3440,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
@@ -4051,7 +4051,7 @@
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
@@ -4662,7 +4662,7 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
@@ -5273,7 +5273,7 @@
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK24" t="inlineStr">
@@ -5884,7 +5884,7 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
@@ -6495,7 +6495,7 @@
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK30" t="inlineStr">
@@ -7106,7 +7106,7 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
@@ -7717,7 +7717,7 @@
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK36" t="inlineStr">
@@ -8328,7 +8328,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK39" t="inlineStr">
@@ -8716,7 +8716,7 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK41" t="inlineStr">
@@ -9104,7 +9104,7 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK43" t="inlineStr">
@@ -9492,7 +9492,7 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK45" t="inlineStr">
@@ -9880,7 +9880,7 @@
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK47" t="inlineStr">
@@ -10268,7 +10268,7 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK49" t="inlineStr">
@@ -10656,7 +10656,7 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK51" t="inlineStr">
@@ -11044,7 +11044,7 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK53" t="inlineStr">
@@ -11432,7 +11432,7 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK55" t="inlineStr">
@@ -11820,7 +11820,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK57" t="inlineStr">
@@ -12208,7 +12208,7 @@
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK59" t="inlineStr">
@@ -12596,7 +12596,7 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK61" t="inlineStr">
@@ -12984,7 +12984,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK63" t="inlineStr">
@@ -13372,7 +13372,7 @@
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK65" t="inlineStr">
@@ -13760,7 +13760,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK67" t="inlineStr">
@@ -14148,7 +14148,7 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK69" t="inlineStr">
@@ -14536,7 +14536,7 @@
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK71" t="inlineStr">
@@ -14924,7 +14924,7 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK73" t="inlineStr">
@@ -15312,7 +15312,7 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK75" t="inlineStr">
@@ -15700,7 +15700,7 @@
       </c>
       <c r="AJ77" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK77" t="inlineStr">
@@ -16088,7 +16088,7 @@
       </c>
       <c r="AJ79" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK79" t="inlineStr">
@@ -16476,7 +16476,7 @@
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK81" t="inlineStr">
@@ -16864,7 +16864,7 @@
       </c>
       <c r="AJ83" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK83" t="inlineStr">
@@ -17252,7 +17252,7 @@
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK85" t="inlineStr">
@@ -17640,7 +17640,7 @@
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK87" t="inlineStr">
@@ -18028,7 +18028,7 @@
       </c>
       <c r="AJ89" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK89" t="inlineStr">
@@ -18416,7 +18416,7 @@
       </c>
       <c r="AJ91" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK91" t="inlineStr">
@@ -18804,7 +18804,7 @@
       </c>
       <c r="AJ93" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK93" t="inlineStr">
@@ -19192,7 +19192,7 @@
       </c>
       <c r="AJ95" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK95" t="inlineStr">
@@ -19580,7 +19580,7 @@
       </c>
       <c r="AJ97" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK97" t="inlineStr">
@@ -19968,7 +19968,7 @@
       </c>
       <c r="AJ99" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK99" t="inlineStr">
@@ -20356,7 +20356,7 @@
       </c>
       <c r="AJ101" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK101" t="inlineStr">
@@ -20744,7 +20744,7 @@
       </c>
       <c r="AJ103" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK103" t="inlineStr">
@@ -21132,7 +21132,7 @@
       </c>
       <c r="AJ105" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK105" t="inlineStr">
@@ -21520,7 +21520,7 @@
       </c>
       <c r="AJ107" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK107" t="inlineStr">
@@ -21908,7 +21908,7 @@
       </c>
       <c r="AJ109" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK109" t="inlineStr">
@@ -22296,7 +22296,7 @@
       </c>
       <c r="AJ111" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK111" t="inlineStr">
@@ -22684,7 +22684,7 @@
       </c>
       <c r="AJ113" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK113" t="inlineStr">
@@ -23072,7 +23072,7 @@
       </c>
       <c r="AJ115" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK115" t="inlineStr">
@@ -23460,7 +23460,7 @@
       </c>
       <c r="AJ117" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK117" t="inlineStr">
@@ -23848,7 +23848,7 @@
       </c>
       <c r="AJ119" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK119" t="inlineStr">
@@ -24236,7 +24236,7 @@
       </c>
       <c r="AJ121" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK121" t="inlineStr">
@@ -24624,7 +24624,7 @@
       </c>
       <c r="AJ123" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK123" t="inlineStr">
@@ -25012,7 +25012,7 @@
       </c>
       <c r="AJ125" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK125" t="inlineStr">
@@ -25400,7 +25400,7 @@
       </c>
       <c r="AJ127" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK127" t="inlineStr">
@@ -25788,7 +25788,7 @@
       </c>
       <c r="AJ129" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK129" t="inlineStr">
@@ -26176,7 +26176,7 @@
       </c>
       <c r="AJ131" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK131" t="inlineStr">
@@ -26564,7 +26564,7 @@
       </c>
       <c r="AJ133" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK133" t="inlineStr">
@@ -26952,7 +26952,7 @@
       </c>
       <c r="AJ135" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK135" t="inlineStr">
@@ -27340,7 +27340,7 @@
       </c>
       <c r="AJ137" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK137" t="inlineStr">
@@ -27728,7 +27728,7 @@
       </c>
       <c r="AJ139" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK139" t="inlineStr">
@@ -28116,7 +28116,7 @@
       </c>
       <c r="AJ141" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK141" t="inlineStr">
@@ -28504,7 +28504,7 @@
       </c>
       <c r="AJ143" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK143" t="inlineStr">
@@ -28892,7 +28892,7 @@
       </c>
       <c r="AJ145" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK145" t="inlineStr">
@@ -29280,7 +29280,7 @@
       </c>
       <c r="AJ147" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK147" t="inlineStr">
@@ -29668,7 +29668,7 @@
       </c>
       <c r="AJ149" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK149" t="inlineStr">
@@ -30056,7 +30056,7 @@
       </c>
       <c r="AJ151" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK151" t="inlineStr">
@@ -30444,7 +30444,7 @@
       </c>
       <c r="AJ153" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK153" t="inlineStr">
@@ -30832,7 +30832,7 @@
       </c>
       <c r="AJ155" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK155" t="inlineStr">
@@ -31220,7 +31220,7 @@
       </c>
       <c r="AJ157" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK157" t="inlineStr">
